--- a/04-ai-governance-and-technical-lifecycle/artifacts/A-24_GenAI_Policy_Compliance_Tracker.xlsx
+++ b/04-ai-governance-and-technical-lifecycle/artifacts/A-24_GenAI_Policy_Compliance_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rityshree\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Career\Portfolio\Project4\Artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915167A5-2CCF-4A73-B9F9-2E9DD493D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DDB7A6-D121-4FE3-A1FE-18477C8E4D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -397,9 +397,6 @@
     <t>Fully Implemented Controls</t>
   </si>
   <si>
-    <t>Controls active in production and verified via effectiveness/config tests</t>
-  </si>
-  <si>
     <t>Constrained Controls (Regional Infrastructure)</t>
   </si>
   <si>
@@ -1105,6 +1102,9 @@
   </si>
   <si>
     <t>Active — Sandbox Only</t>
+  </si>
+  <si>
+    <t>Controls specified as active, with effectiveness/config test methods defined</t>
   </si>
 </sst>
 </file>
@@ -2350,43 +2350,43 @@
         <v>16</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
         <f>COUNTIF(E5:E21,"CONSTRAINED")</f>
         <v>1</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B30" s="6">
         <f>COUNTIF(E5:E21,"Outstanding")</f>
         <v>0</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="12">
         <f>IF(B24=0,0,B28/B24)</f>
         <v>0.94117647058823528</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2412,12 +2412,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -2425,28 +2425,28 @@
         <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -2454,28 +2454,28 @@
         <v>65</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2496,12 +2496,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,13 +2509,13 @@
         <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,13 +2523,13 @@
         <v>41</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,13 +2537,13 @@
         <v>49</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" x14ac:dyDescent="0.3">
@@ -2551,13 +2551,13 @@
         <v>51</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,13 +2565,13 @@
         <v>55</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2579,13 +2579,13 @@
         <v>59</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -2593,13 +2593,13 @@
         <v>65</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" x14ac:dyDescent="0.3">
@@ -2607,13 +2607,13 @@
         <v>72</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2621,13 +2621,13 @@
         <v>74</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="25.2" x14ac:dyDescent="0.3">
@@ -2635,13 +2635,13 @@
         <v>77</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -2649,13 +2649,13 @@
         <v>80</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2663,13 +2663,13 @@
         <v>83</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="25.2" x14ac:dyDescent="0.3">
@@ -2677,13 +2677,13 @@
         <v>88</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2691,13 +2691,13 @@
         <v>91</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.2" x14ac:dyDescent="0.3">
@@ -2705,13 +2705,13 @@
         <v>96</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.2" x14ac:dyDescent="0.3">
@@ -2719,13 +2719,13 @@
         <v>99</v>
       </c>
       <c r="B19" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2733,13 +2733,13 @@
         <v>102</v>
       </c>
       <c r="B20" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2747,13 +2747,13 @@
         <v>104</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2778,38 +2778,38 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>18</v>
@@ -2817,234 +2817,234 @@
     </row>
     <row r="5" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="I6" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>223</v>
-      </c>
       <c r="I7" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>229</v>
-      </c>
       <c r="I8" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="C11" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="14" t="s">
         <v>253</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="C12" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="14" t="s">
         <v>262</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3072,44 +3072,44 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>18</v>
@@ -3117,142 +3117,142 @@
     </row>
     <row r="5" spans="1:11" ht="48" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="8" t="s">
         <v>284</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="48" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>305</v>
-      </c>
       <c r="K7" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="48" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="F8" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="K8" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3278,41 +3278,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>18</v>
@@ -3320,98 +3320,98 @@
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>327</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="15" t="s">
         <v>333</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="48" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>354</v>
       </c>
     </row>
   </sheetData>
